--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122385267</v>
       </c>
       <c r="B2" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387985</v>
+        <v>122387659</v>
       </c>
       <c r="B3" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590101</v>
+        <v>590096</v>
       </c>
       <c r="R3" t="n">
-        <v>6441312</v>
+        <v>6441257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387614</v>
+        <v>122388005</v>
       </c>
       <c r="B4" t="n">
-        <v>57744</v>
+        <v>105290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,31 +927,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590099</v>
+        <v>590151</v>
       </c>
       <c r="R4" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,6 +1013,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122388079</v>
+        <v>122388085</v>
       </c>
       <c r="B5" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590177</v>
+        <v>590192</v>
       </c>
       <c r="R5" t="n">
-        <v>6441260</v>
+        <v>6441252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387599</v>
+        <v>122387614</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>57744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,35 +1155,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1190,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590106</v>
+        <v>590099</v>
       </c>
       <c r="R6" t="n">
-        <v>6441255</v>
+        <v>6441240</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1245,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1263,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122388005</v>
+        <v>122387985</v>
       </c>
       <c r="B7" t="n">
-        <v>105280</v>
+        <v>98185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,25 +1275,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590151</v>
+        <v>590101</v>
       </c>
       <c r="R7" t="n">
-        <v>6441271</v>
+        <v>6441312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388002</v>
+        <v>122387610</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>57527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,35 +1396,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1432,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590103</v>
+        <v>590099</v>
       </c>
       <c r="R8" t="n">
-        <v>6441302</v>
+        <v>6441240</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1490,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1505,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387610</v>
+        <v>122387599</v>
       </c>
       <c r="B9" t="n">
-        <v>57527</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,39 +1520,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1557,13 +1556,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590099</v>
+        <v>590106</v>
       </c>
       <c r="R9" t="n">
-        <v>6441240</v>
+        <v>6441255</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,6 +1610,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387659</v>
+        <v>122387641</v>
       </c>
       <c r="B10" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,14 +1673,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590096</v>
+        <v>590098</v>
       </c>
       <c r="R10" t="n">
-        <v>6441257</v>
+        <v>6441232</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388072</v>
+        <v>122388002</v>
       </c>
       <c r="B11" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590170</v>
+        <v>590103</v>
       </c>
       <c r="R11" t="n">
-        <v>6441271</v>
+        <v>6441302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,9 +1831,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122388085</v>
+        <v>122388079</v>
       </c>
       <c r="B12" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1909,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590192</v>
+        <v>590177</v>
       </c>
       <c r="R12" t="n">
-        <v>6441252</v>
+        <v>6441260</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1972,10 +1982,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385241</v>
+        <v>122388072</v>
       </c>
       <c r="B13" t="n">
-        <v>105241</v>
+        <v>98185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,32 +1994,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2020,17 +2026,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590097</v>
+        <v>590170</v>
       </c>
       <c r="R13" t="n">
-        <v>6441248</v>
+        <v>6441271</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2075,22 +2081,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122387641</v>
+        <v>122385241</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>105251</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,28 +2105,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2131,17 +2141,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590098</v>
+        <v>590097</v>
       </c>
       <c r="R14" t="n">
-        <v>6441232</v>
+        <v>6441248</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2168,19 +2178,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,15 +2196,348 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122435277</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105290</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A1779, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>590194</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6441232</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122435344</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98185</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 2806, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>590106</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6441250</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122435302</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105290</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 2806, Svartgöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>590129</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6441267</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122385267</v>
+        <v>122385241</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>105251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590207</v>
+        <v>590097</v>
       </c>
       <c r="R2" t="n">
-        <v>6441245</v>
+        <v>6441248</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387659</v>
+        <v>122387599</v>
       </c>
       <c r="B3" t="n">
         <v>98185</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590096</v>
+        <v>590106</v>
       </c>
       <c r="R3" t="n">
-        <v>6441257</v>
+        <v>6441255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122388005</v>
+        <v>122388072</v>
       </c>
       <c r="B4" t="n">
-        <v>105290</v>
+        <v>98185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590151</v>
+        <v>590170</v>
       </c>
       <c r="R4" t="n">
         <v>6441271</v>
@@ -992,19 +992,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122388085</v>
+        <v>122387614</v>
       </c>
       <c r="B5" t="n">
-        <v>98185</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,35 +1034,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590192</v>
+        <v>590099</v>
       </c>
       <c r="R5" t="n">
-        <v>6441252</v>
+        <v>6441240</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,18 +1103,27 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387614</v>
+        <v>122385267</v>
       </c>
       <c r="B6" t="n">
-        <v>57744</v>
+        <v>90789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,49 +1154,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590099</v>
+        <v>590207</v>
       </c>
       <c r="R6" t="n">
-        <v>6441240</v>
+        <v>6441245</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,19 +1222,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,28 +1238,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387985</v>
+        <v>122388005</v>
       </c>
       <c r="B7" t="n">
-        <v>98185</v>
+        <v>105290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1311,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590101</v>
+        <v>590151</v>
       </c>
       <c r="R7" t="n">
-        <v>6441312</v>
+        <v>6441271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387610</v>
+        <v>122388002</v>
       </c>
       <c r="B8" t="n">
-        <v>57527</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,39 +1390,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1436,13 +1426,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590099</v>
+        <v>590103</v>
       </c>
       <c r="R8" t="n">
-        <v>6441240</v>
+        <v>6441302</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,6 +1480,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1508,7 +1499,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387599</v>
+        <v>122388079</v>
       </c>
       <c r="B9" t="n">
         <v>98185</v>
@@ -1556,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590106</v>
+        <v>590177</v>
       </c>
       <c r="R9" t="n">
-        <v>6441255</v>
+        <v>6441260</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,19 +1580,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,7 +1610,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387641</v>
+        <v>122387985</v>
       </c>
       <c r="B10" t="n">
         <v>98185</v>
@@ -1673,14 +1654,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590098</v>
+        <v>590101</v>
       </c>
       <c r="R10" t="n">
-        <v>6441232</v>
+        <v>6441312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,7 +1731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388002</v>
+        <v>122388085</v>
       </c>
       <c r="B11" t="n">
         <v>98185</v>
@@ -1798,10 +1779,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590103</v>
+        <v>590192</v>
       </c>
       <c r="R11" t="n">
-        <v>6441302</v>
+        <v>6441252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,19 +1812,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,7 +1842,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122388079</v>
+        <v>122387659</v>
       </c>
       <c r="B12" t="n">
         <v>98185</v>
@@ -1919,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590177</v>
+        <v>590096</v>
       </c>
       <c r="R12" t="n">
-        <v>6441260</v>
+        <v>6441257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1952,9 +1923,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,7 +1963,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122388072</v>
+        <v>122387641</v>
       </c>
       <c r="B13" t="n">
         <v>98185</v>
@@ -2026,14 +2007,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590170</v>
+        <v>590098</v>
       </c>
       <c r="R13" t="n">
-        <v>6441271</v>
+        <v>6441232</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,9 +2044,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2084,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385241</v>
+        <v>122387610</v>
       </c>
       <c r="B14" t="n">
-        <v>105251</v>
+        <v>57527</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,53 +2096,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>340</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590097</v>
+        <v>590099</v>
       </c>
       <c r="R14" t="n">
-        <v>6441248</v>
+        <v>6441240</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2178,30 +2169,39 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435344</v>
+        <v>122435302</v>
       </c>
       <c r="B16" t="n">
-        <v>98185</v>
+        <v>105290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590106</v>
+        <v>590129</v>
       </c>
       <c r="R16" t="n">
-        <v>6441250</v>
+        <v>6441267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B17" t="n">
-        <v>105290</v>
+        <v>98185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,25 +2442,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R17" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2538,6 +2538,131 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122449135</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105251</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>340</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öndal, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590097</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6441254</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Hf-Väs-1974</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Åke Rühling</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122385241</v>
+        <v>122388005</v>
       </c>
       <c r="B2" t="n">
-        <v>105251</v>
+        <v>105303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590097</v>
+        <v>590151</v>
       </c>
       <c r="R2" t="n">
-        <v>6441248</v>
+        <v>6441271</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,9 +756,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387599</v>
+        <v>122385267</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>90801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,49 +808,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590106</v>
+        <v>590207</v>
       </c>
       <c r="R3" t="n">
-        <v>6441255</v>
+        <v>6441245</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,19 +876,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +899,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122388072</v>
+        <v>122387614</v>
       </c>
       <c r="B4" t="n">
-        <v>98185</v>
+        <v>57749</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,35 +923,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590170</v>
+        <v>590099</v>
       </c>
       <c r="R4" t="n">
-        <v>6441271</v>
+        <v>6441240</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,18 +992,27 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387614</v>
+        <v>122385241</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>105264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,49 +1043,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>340</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590099</v>
+        <v>590097</v>
       </c>
       <c r="R5" t="n">
-        <v>6441240</v>
+        <v>6441248</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,49 +1116,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385267</v>
+        <v>122387659</v>
       </c>
       <c r="B6" t="n">
-        <v>90789</v>
+        <v>98197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,48 +1158,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590207</v>
+        <v>590096</v>
       </c>
       <c r="R6" t="n">
-        <v>6441245</v>
+        <v>6441257</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,14 +1227,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,22 +1255,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122388005</v>
+        <v>122387610</v>
       </c>
       <c r="B7" t="n">
-        <v>105290</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,35 +1279,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1305,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590151</v>
+        <v>590099</v>
       </c>
       <c r="R7" t="n">
-        <v>6441271</v>
+        <v>6441240</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1373,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1378,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388002</v>
+        <v>122388085</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590103</v>
+        <v>590192</v>
       </c>
       <c r="R8" t="n">
-        <v>6441302</v>
+        <v>6441252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,19 +1472,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,7 +1505,7 @@
         <v>122388079</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1610,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387985</v>
+        <v>122387641</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1654,14 +1657,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590101</v>
+        <v>590098</v>
       </c>
       <c r="R10" t="n">
-        <v>6441312</v>
+        <v>6441232</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388085</v>
+        <v>122388002</v>
       </c>
       <c r="B11" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590192</v>
+        <v>590103</v>
       </c>
       <c r="R11" t="n">
-        <v>6441252</v>
+        <v>6441302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,9 +1815,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387659</v>
+        <v>122387599</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590096</v>
+        <v>590106</v>
       </c>
       <c r="R12" t="n">
-        <v>6441257</v>
+        <v>6441255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1963,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387641</v>
+        <v>122387985</v>
       </c>
       <c r="B13" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,14 +2020,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590098</v>
+        <v>590101</v>
       </c>
       <c r="R13" t="n">
-        <v>6441232</v>
+        <v>6441312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2084,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122387610</v>
+        <v>122388072</v>
       </c>
       <c r="B14" t="n">
-        <v>57527</v>
+        <v>98197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,39 +2109,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2136,13 +2145,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590099</v>
+        <v>590170</v>
       </c>
       <c r="R14" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2169,27 +2178,18 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435277</v>
+        <v>122435302</v>
       </c>
       <c r="B15" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,14 +2252,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590194</v>
+        <v>590129</v>
       </c>
       <c r="R15" t="n">
-        <v>6441232</v>
+        <v>6441267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B16" t="n">
-        <v>105290</v>
+        <v>98197</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R16" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435344</v>
+        <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>98185</v>
+        <v>105303</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,25 +2442,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590106</v>
+        <v>590194</v>
       </c>
       <c r="R17" t="n">
-        <v>6441250</v>
+        <v>6441232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105251</v>
+        <v>105264</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122388005</v>
       </c>
       <c r="B2" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122385267</v>
+        <v>122388079</v>
       </c>
       <c r="B3" t="n">
-        <v>90801</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,48 +808,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590207</v>
+        <v>590177</v>
       </c>
       <c r="R3" t="n">
-        <v>6441245</v>
+        <v>6441260</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,11 +880,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +895,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387614</v>
+        <v>122387985</v>
       </c>
       <c r="B4" t="n">
-        <v>57749</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,35 +919,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590099</v>
+        <v>590101</v>
       </c>
       <c r="R4" t="n">
-        <v>6441240</v>
+        <v>6441312</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122385241</v>
+        <v>122388072</v>
       </c>
       <c r="B5" t="n">
-        <v>105264</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,32 +1040,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1079,17 +1072,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590097</v>
+        <v>590170</v>
       </c>
       <c r="R5" t="n">
-        <v>6441248</v>
+        <v>6441271</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,22 +1127,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387659</v>
+        <v>122385267</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>90808</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,49 +1151,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590096</v>
+        <v>590207</v>
       </c>
       <c r="R6" t="n">
-        <v>6441257</v>
+        <v>6441245</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,19 +1219,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387610</v>
+        <v>122388002</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,39 +1266,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590099</v>
+        <v>590103</v>
       </c>
       <c r="R7" t="n">
-        <v>6441240</v>
+        <v>6441302</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,6 +1356,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1394,7 +1378,7 @@
         <v>122388085</v>
       </c>
       <c r="B8" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1502,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388079</v>
+        <v>122385241</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>105269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,28 +1498,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1546,17 +1534,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590177</v>
+        <v>590097</v>
       </c>
       <c r="R9" t="n">
-        <v>6441260</v>
+        <v>6441248</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387641</v>
+        <v>122387614</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>57749</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,49 +1613,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590098</v>
+        <v>590099</v>
       </c>
       <c r="R10" t="n">
-        <v>6441232</v>
+        <v>6441240</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1715,7 +1703,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1734,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388002</v>
+        <v>122387659</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1782,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590103</v>
+        <v>590096</v>
       </c>
       <c r="R11" t="n">
-        <v>6441302</v>
+        <v>6441257</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1855,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387599</v>
+        <v>122387610</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>57532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,35 +1854,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1903,13 +1894,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590106</v>
+        <v>590099</v>
       </c>
       <c r="R12" t="n">
-        <v>6441255</v>
+        <v>6441240</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1957,7 +1948,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1976,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387985</v>
+        <v>122387599</v>
       </c>
       <c r="B13" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590101</v>
+        <v>590106</v>
       </c>
       <c r="R13" t="n">
-        <v>6441312</v>
+        <v>6441255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2097,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122388072</v>
+        <v>122387641</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,14 +2131,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590170</v>
+        <v>590098</v>
       </c>
       <c r="R14" t="n">
-        <v>6441271</v>
+        <v>6441232</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,9 +2168,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,7 +2211,7 @@
         <v>122435302</v>
       </c>
       <c r="B15" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>122435344</v>
       </c>
       <c r="B16" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105264</v>
+        <v>105269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385267</v>
+        <v>122385241</v>
       </c>
       <c r="B6" t="n">
-        <v>90808</v>
+        <v>105269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,34 +1151,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>340</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590207</v>
+        <v>590097</v>
       </c>
       <c r="R6" t="n">
-        <v>6441245</v>
+        <v>6441248</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,11 +1227,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122388002</v>
+        <v>122385267</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>90808</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,49 +1266,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590103</v>
+        <v>590207</v>
       </c>
       <c r="R7" t="n">
-        <v>6441302</v>
+        <v>6441245</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,19 +1334,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,19 +1357,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388085</v>
+        <v>122388002</v>
       </c>
       <c r="B8" t="n">
         <v>98202</v>
@@ -1423,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590192</v>
+        <v>590103</v>
       </c>
       <c r="R8" t="n">
-        <v>6441252</v>
+        <v>6441302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,9 +1450,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122385241</v>
+        <v>122388085</v>
       </c>
       <c r="B9" t="n">
-        <v>105269</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,32 +1502,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1534,17 +1534,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590097</v>
+        <v>590192</v>
       </c>
       <c r="R9" t="n">
-        <v>6441248</v>
+        <v>6441252</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385241</v>
+        <v>122385267</v>
       </c>
       <c r="B6" t="n">
-        <v>105269</v>
+        <v>90808</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,39 +1151,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590097</v>
+        <v>590207</v>
       </c>
       <c r="R6" t="n">
-        <v>6441248</v>
+        <v>6441245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,6 +1222,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122385267</v>
+        <v>122388002</v>
       </c>
       <c r="B7" t="n">
-        <v>90808</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,48 +1266,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590207</v>
+        <v>590103</v>
       </c>
       <c r="R7" t="n">
-        <v>6441245</v>
+        <v>6441302</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,14 +1335,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,19 +1363,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388002</v>
+        <v>122388085</v>
       </c>
       <c r="B8" t="n">
         <v>98202</v>
@@ -1417,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590103</v>
+        <v>590192</v>
       </c>
       <c r="R8" t="n">
-        <v>6441302</v>
+        <v>6441252</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,19 +1456,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388085</v>
+        <v>122385241</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>105269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,28 +1498,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1534,17 +1534,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590192</v>
+        <v>590097</v>
       </c>
       <c r="R9" t="n">
-        <v>6441252</v>
+        <v>6441248</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B15" t="n">
-        <v>105308</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R15" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435344</v>
+        <v>122435302</v>
       </c>
       <c r="B16" t="n">
-        <v>98202</v>
+        <v>105308</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590106</v>
+        <v>590129</v>
       </c>
       <c r="R16" t="n">
-        <v>6441250</v>
+        <v>6441267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122388005</v>
+        <v>122388085</v>
       </c>
       <c r="B2" t="n">
-        <v>105308</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590151</v>
+        <v>590192</v>
       </c>
       <c r="R2" t="n">
-        <v>6441271</v>
+        <v>6441252</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +751,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388079</v>
+        <v>122387659</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,11 +798,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590177</v>
+        <v>590096</v>
       </c>
       <c r="R3" t="n">
-        <v>6441260</v>
+        <v>6441257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,9 +857,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387985</v>
+        <v>122388002</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,11 +914,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -955,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590101</v>
+        <v>590103</v>
       </c>
       <c r="R4" t="n">
-        <v>6441312</v>
+        <v>6441302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122388072</v>
+        <v>122387599</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,11 +1030,6 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1076,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590170</v>
+        <v>590106</v>
       </c>
       <c r="R5" t="n">
-        <v>6441271</v>
+        <v>6441255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,9 +1089,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385267</v>
+        <v>122385241</v>
       </c>
       <c r="B6" t="n">
-        <v>90808</v>
+        <v>105278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,34 +1141,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>340</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1186,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590207</v>
+        <v>590097</v>
       </c>
       <c r="R6" t="n">
-        <v>6441245</v>
+        <v>6441248</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1222,11 +1212,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122388002</v>
+        <v>122387641</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,11 +1256,6 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1298,14 +1278,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590103</v>
+        <v>590098</v>
       </c>
       <c r="R7" t="n">
-        <v>6441302</v>
+        <v>6441232</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1375,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388085</v>
+        <v>122387614</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>57749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,35 +1367,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590192</v>
+        <v>590099</v>
       </c>
       <c r="R8" t="n">
-        <v>6441252</v>
+        <v>6441240</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,18 +1431,27 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1486,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122385241</v>
+        <v>122388005</v>
       </c>
       <c r="B9" t="n">
-        <v>105269</v>
+        <v>105317</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,32 +1482,23 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>340</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1534,17 +1509,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590097</v>
+        <v>590151</v>
       </c>
       <c r="R9" t="n">
-        <v>6441248</v>
+        <v>6441271</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,9 +1546,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387614</v>
+        <v>122388079</v>
       </c>
       <c r="B10" t="n">
-        <v>57749</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,35 +1598,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1649,13 +1629,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590099</v>
+        <v>590177</v>
       </c>
       <c r="R10" t="n">
-        <v>6441240</v>
+        <v>6441260</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,27 +1662,18 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1721,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387659</v>
+        <v>122385267</v>
       </c>
       <c r="B11" t="n">
-        <v>98202</v>
+        <v>90813</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,49 +1704,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590096</v>
+        <v>590207</v>
       </c>
       <c r="R11" t="n">
-        <v>6441257</v>
+        <v>6441245</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,19 +1767,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,12 +1790,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1860,11 +1820,6 @@
       <c r="E12" t="n">
         <v>103021</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -1966,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387599</v>
+        <v>122388072</v>
       </c>
       <c r="B13" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,11 +1938,6 @@
       </c>
       <c r="E13" t="n">
         <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2014,10 +1964,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590106</v>
+        <v>590170</v>
       </c>
       <c r="R13" t="n">
-        <v>6441255</v>
+        <v>6441271</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,19 +1997,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122387641</v>
+        <v>122387985</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,11 +2044,6 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2131,14 +2066,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590098</v>
+        <v>590101</v>
       </c>
       <c r="R14" t="n">
-        <v>6441232</v>
+        <v>6441312</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2208,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435344</v>
+        <v>122435302</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>105317</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2155,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590106</v>
+        <v>590129</v>
       </c>
       <c r="R15" t="n">
-        <v>6441250</v>
+        <v>6441267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435302</v>
+        <v>122435277</v>
       </c>
       <c r="B16" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,11 +2266,6 @@
       </c>
       <c r="E16" t="n">
         <v>221144</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2363,14 +2288,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590129</v>
+        <v>590194</v>
       </c>
       <c r="R16" t="n">
-        <v>6441267</v>
+        <v>6441232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435277</v>
+        <v>122435344</v>
       </c>
       <c r="B17" t="n">
-        <v>105308</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,25 +2367,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,14 +2394,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590194</v>
+        <v>590106</v>
       </c>
       <c r="R17" t="n">
-        <v>6441232</v>
+        <v>6441250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2464,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105269</v>
+        <v>105278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,11 +2478,6 @@
       </c>
       <c r="E18" t="n">
         <v>340</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ryl</t>
-        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387614</v>
+        <v>122388005</v>
       </c>
       <c r="B8" t="n">
-        <v>57749</v>
+        <v>105317</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,26 +1371,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590099</v>
+        <v>590151</v>
       </c>
       <c r="R8" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,6 +1452,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1470,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388005</v>
+        <v>122387614</v>
       </c>
       <c r="B9" t="n">
-        <v>105317</v>
+        <v>57749</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,26 +1487,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1513,13 +1514,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590151</v>
+        <v>590099</v>
       </c>
       <c r="R9" t="n">
-        <v>6441271</v>
+        <v>6441240</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1568,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388005</v>
+        <v>122387614</v>
       </c>
       <c r="B8" t="n">
-        <v>105317</v>
+        <v>57749</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,26 +1371,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590151</v>
+        <v>590099</v>
       </c>
       <c r="R8" t="n">
-        <v>6441271</v>
+        <v>6441240</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1452,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1471,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387614</v>
+        <v>122388005</v>
       </c>
       <c r="B9" t="n">
-        <v>57749</v>
+        <v>105317</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,26 +1486,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1514,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590099</v>
+        <v>590151</v>
       </c>
       <c r="R9" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,6 +1567,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122388085</v>
+        <v>122388072</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590192</v>
+        <v>590170</v>
       </c>
       <c r="R2" t="n">
-        <v>6441252</v>
+        <v>6441271</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387659</v>
+        <v>122388085</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,6 +803,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -824,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590096</v>
+        <v>590192</v>
       </c>
       <c r="R3" t="n">
-        <v>6441257</v>
+        <v>6441252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +867,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122388002</v>
+        <v>122385267</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>90826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,44 +909,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590103</v>
+        <v>590207</v>
       </c>
       <c r="R4" t="n">
-        <v>6441302</v>
+        <v>6441245</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,19 +977,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,12 +1000,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1016,7 +1015,7 @@
         <v>122387599</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,6 +1029,11 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1132,7 +1136,7 @@
         <v>122385241</v>
       </c>
       <c r="B6" t="n">
-        <v>105278</v>
+        <v>105291</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,6 +1150,11 @@
       </c>
       <c r="E6" t="n">
         <v>340</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1242,7 +1251,7 @@
         <v>122387641</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,6 +1265,11 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1355,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387614</v>
+        <v>122387659</v>
       </c>
       <c r="B8" t="n">
-        <v>57749</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,30 +1381,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590099</v>
+        <v>590096</v>
       </c>
       <c r="R8" t="n">
-        <v>6441240</v>
+        <v>6441257</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,6 +1471,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,7 +1493,7 @@
         <v>122388005</v>
       </c>
       <c r="B9" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,6 +1507,11 @@
       </c>
       <c r="E9" t="n">
         <v>221144</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1589,7 +1614,7 @@
         <v>122388079</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,6 +1628,11 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1692,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385267</v>
+        <v>122387614</v>
       </c>
       <c r="B11" t="n">
-        <v>90813</v>
+        <v>57753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,43 +1734,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590207</v>
+        <v>590099</v>
       </c>
       <c r="R11" t="n">
-        <v>6441245</v>
+        <v>6441240</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,14 +1803,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,19 +1824,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1805,7 +1845,7 @@
         <v>122387610</v>
       </c>
       <c r="B12" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,6 +1859,11 @@
       </c>
       <c r="E12" t="n">
         <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1921,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122388072</v>
+        <v>122388002</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,6 +1983,11 @@
       </c>
       <c r="E13" t="n">
         <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1964,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590170</v>
+        <v>590103</v>
       </c>
       <c r="R13" t="n">
-        <v>6441271</v>
+        <v>6441302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,9 +2047,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,7 +2090,7 @@
         <v>122387985</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,6 +2104,11 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2146,7 +2211,7 @@
         <v>122435302</v>
       </c>
       <c r="B15" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,6 +2225,11 @@
       </c>
       <c r="E15" t="n">
         <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2249,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435277</v>
+        <v>122435344</v>
       </c>
       <c r="B16" t="n">
-        <v>105317</v>
+        <v>98224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,20 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590194</v>
+        <v>590106</v>
       </c>
       <c r="R16" t="n">
-        <v>6441232</v>
+        <v>6441250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435344</v>
+        <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>105330</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,20 +2442,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590106</v>
+        <v>590194</v>
       </c>
       <c r="R17" t="n">
-        <v>6441250</v>
+        <v>6441232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105278</v>
+        <v>105291</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,6 +2558,11 @@
       </c>
       <c r="E18" t="n">
         <v>340</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122388072</v>
+        <v>122387599</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590170</v>
+        <v>590106</v>
       </c>
       <c r="R2" t="n">
-        <v>6441271</v>
+        <v>6441255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,9 +756,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388085</v>
+        <v>122388072</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590192</v>
+        <v>590170</v>
       </c>
       <c r="R3" t="n">
-        <v>6441252</v>
+        <v>6441271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122385267</v>
+        <v>122387641</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,48 +919,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590207</v>
+        <v>590098</v>
       </c>
       <c r="R4" t="n">
-        <v>6441245</v>
+        <v>6441232</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,14 +988,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,22 +1016,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387599</v>
+        <v>122388002</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590106</v>
+        <v>590103</v>
       </c>
       <c r="R5" t="n">
-        <v>6441255</v>
+        <v>6441302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385241</v>
+        <v>122387610</v>
       </c>
       <c r="B6" t="n">
-        <v>105291</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,53 +1161,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590097</v>
+        <v>590099</v>
       </c>
       <c r="R6" t="n">
-        <v>6441248</v>
+        <v>6441240</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,40 +1234,49 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387641</v>
+        <v>122387985</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,14 +1317,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590098</v>
+        <v>590101</v>
       </c>
       <c r="R7" t="n">
-        <v>6441232</v>
+        <v>6441312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387659</v>
+        <v>122388005</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>105343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,25 +1406,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1442,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590096</v>
+        <v>590151</v>
       </c>
       <c r="R8" t="n">
-        <v>6441257</v>
+        <v>6441271</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388005</v>
+        <v>122388085</v>
       </c>
       <c r="B9" t="n">
-        <v>105330</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,25 +1527,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590151</v>
+        <v>590192</v>
       </c>
       <c r="R9" t="n">
-        <v>6441271</v>
+        <v>6441252</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,19 +1596,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122388079</v>
+        <v>122387659</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590177</v>
+        <v>590096</v>
       </c>
       <c r="R10" t="n">
-        <v>6441260</v>
+        <v>6441257</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,9 +1707,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387614</v>
+        <v>122385267</v>
       </c>
       <c r="B11" t="n">
-        <v>57753</v>
+        <v>90839</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,49 +1759,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590099</v>
+        <v>590207</v>
       </c>
       <c r="R11" t="n">
-        <v>6441240</v>
+        <v>6441245</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,19 +1827,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,28 +1843,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387610</v>
+        <v>122385241</v>
       </c>
       <c r="B12" t="n">
-        <v>57536</v>
+        <v>105304</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,53 +1874,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>340</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590099</v>
+        <v>590097</v>
       </c>
       <c r="R12" t="n">
-        <v>6441240</v>
+        <v>6441248</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,49 +1947,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122388002</v>
+        <v>122388079</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590103</v>
+        <v>590177</v>
       </c>
       <c r="R13" t="n">
-        <v>6441302</v>
+        <v>6441260</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,19 +2058,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122387985</v>
+        <v>122387614</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>57753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,35 +2100,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2135,13 +2136,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590101</v>
+        <v>590099</v>
       </c>
       <c r="R14" t="n">
-        <v>6441312</v>
+        <v>6441240</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2189,7 +2190,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B15" t="n">
-        <v>105330</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R15" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435344</v>
+        <v>122435277</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>105343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590106</v>
+        <v>590194</v>
       </c>
       <c r="R16" t="n">
-        <v>6441250</v>
+        <v>6441232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435277</v>
+        <v>122435302</v>
       </c>
       <c r="B17" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590194</v>
+        <v>590129</v>
       </c>
       <c r="R17" t="n">
-        <v>6441232</v>
+        <v>6441267</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105291</v>
+        <v>105304</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387610</v>
+        <v>122387985</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,39 +1161,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1201,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590099</v>
+        <v>590101</v>
       </c>
       <c r="R6" t="n">
-        <v>6441240</v>
+        <v>6441312</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,6 +1251,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387985</v>
+        <v>122387610</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,35 +1282,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590101</v>
+        <v>590099</v>
       </c>
       <c r="R7" t="n">
-        <v>6441312</v>
+        <v>6441240</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1375,7 +1376,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122387599</v>
+        <v>122388002</v>
       </c>
       <c r="B2" t="n">
         <v>98237</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590106</v>
+        <v>590103</v>
       </c>
       <c r="R2" t="n">
-        <v>6441255</v>
+        <v>6441302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388072</v>
+        <v>122388079</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590170</v>
+        <v>590177</v>
       </c>
       <c r="R3" t="n">
-        <v>6441271</v>
+        <v>6441260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387641</v>
+        <v>122388005</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,14 +951,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590098</v>
+        <v>590151</v>
       </c>
       <c r="R4" t="n">
-        <v>6441232</v>
+        <v>6441271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122388002</v>
+        <v>122387610</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,35 +1040,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590103</v>
+        <v>590099</v>
       </c>
       <c r="R5" t="n">
-        <v>6441302</v>
+        <v>6441240</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1134,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1270,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387610</v>
+        <v>122387659</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,39 +1285,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,13 +1321,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590099</v>
+        <v>590096</v>
       </c>
       <c r="R7" t="n">
-        <v>6441240</v>
+        <v>6441257</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,6 +1375,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122388005</v>
+        <v>122385241</v>
       </c>
       <c r="B8" t="n">
-        <v>105343</v>
+        <v>105304</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,28 +1406,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>340</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1438,17 +1442,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590151</v>
+        <v>590097</v>
       </c>
       <c r="R8" t="n">
-        <v>6441271</v>
+        <v>6441248</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1475,19 +1479,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,19 +1497,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388085</v>
+        <v>122387641</v>
       </c>
       <c r="B9" t="n">
         <v>98237</v>
@@ -1559,14 +1553,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590192</v>
+        <v>590098</v>
       </c>
       <c r="R9" t="n">
-        <v>6441252</v>
+        <v>6441232</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,9 +1590,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,7 +1630,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387659</v>
+        <v>122387599</v>
       </c>
       <c r="B10" t="n">
         <v>98237</v>
@@ -1674,10 +1678,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590096</v>
+        <v>590106</v>
       </c>
       <c r="R10" t="n">
-        <v>6441257</v>
+        <v>6441255</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385267</v>
+        <v>122387614</v>
       </c>
       <c r="B11" t="n">
-        <v>90839</v>
+        <v>57753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,48 +1763,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590207</v>
+        <v>590099</v>
       </c>
       <c r="R11" t="n">
-        <v>6441245</v>
+        <v>6441240</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1827,14 +1832,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,29 +1853,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385241</v>
+        <v>122388072</v>
       </c>
       <c r="B12" t="n">
-        <v>105304</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,32 +1883,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1910,17 +1915,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590097</v>
+        <v>590170</v>
       </c>
       <c r="R12" t="n">
-        <v>6441248</v>
+        <v>6441271</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1965,19 +1970,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122388079</v>
+        <v>122388085</v>
       </c>
       <c r="B13" t="n">
         <v>98237</v>
@@ -2025,10 +2030,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590177</v>
+        <v>590192</v>
       </c>
       <c r="R13" t="n">
-        <v>6441260</v>
+        <v>6441252</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2088,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122387614</v>
+        <v>122385267</v>
       </c>
       <c r="B14" t="n">
-        <v>57753</v>
+        <v>90839</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,49 +2105,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590099</v>
+        <v>590207</v>
       </c>
       <c r="R14" t="n">
-        <v>6441240</v>
+        <v>6441245</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2169,19 +2173,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,28 +2189,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435344</v>
+        <v>122435302</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590106</v>
+        <v>590129</v>
       </c>
       <c r="R15" t="n">
-        <v>6441250</v>
+        <v>6441267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B17" t="n">
-        <v>105343</v>
+        <v>98237</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,25 +2442,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R17" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387985</v>
+        <v>122385241</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>105304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,28 +1164,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1196,17 +1200,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590101</v>
+        <v>590097</v>
       </c>
       <c r="R6" t="n">
-        <v>6441312</v>
+        <v>6441248</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,19 +1237,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,19 +1255,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387659</v>
+        <v>122387985</v>
       </c>
       <c r="B7" t="n">
         <v>98237</v>
@@ -1321,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590096</v>
+        <v>590101</v>
       </c>
       <c r="R7" t="n">
-        <v>6441257</v>
+        <v>6441312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1394,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122385241</v>
+        <v>122387659</v>
       </c>
       <c r="B8" t="n">
-        <v>105304</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,32 +1400,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1442,17 +1432,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590097</v>
+        <v>590096</v>
       </c>
       <c r="R8" t="n">
-        <v>6441248</v>
+        <v>6441257</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1479,9 +1469,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,12 +1497,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122388002</v>
+        <v>122387641</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590103</v>
+        <v>590098</v>
       </c>
       <c r="R2" t="n">
-        <v>6441302</v>
+        <v>6441232</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388079</v>
+        <v>122388085</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590177</v>
+        <v>590192</v>
       </c>
       <c r="R3" t="n">
-        <v>6441260</v>
+        <v>6441252</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122388005</v>
+        <v>122387985</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590151</v>
+        <v>590101</v>
       </c>
       <c r="R4" t="n">
-        <v>6441271</v>
+        <v>6441312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387610</v>
+        <v>122387659</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,39 +1040,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590099</v>
+        <v>590096</v>
       </c>
       <c r="R5" t="n">
-        <v>6441240</v>
+        <v>6441257</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,6 +1130,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1152,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385241</v>
+        <v>122388079</v>
       </c>
       <c r="B6" t="n">
-        <v>105304</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,32 +1161,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1200,17 +1193,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590097</v>
+        <v>590177</v>
       </c>
       <c r="R6" t="n">
-        <v>6441248</v>
+        <v>6441260</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387985</v>
+        <v>122388002</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1315,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590101</v>
+        <v>590103</v>
       </c>
       <c r="R7" t="n">
-        <v>6441312</v>
+        <v>6441302</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387659</v>
+        <v>122385241</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>105307</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,28 +1393,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1432,17 +1429,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590096</v>
+        <v>590097</v>
       </c>
       <c r="R8" t="n">
-        <v>6441257</v>
+        <v>6441248</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,19 +1466,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,22 +1484,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387641</v>
+        <v>122387610</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,49 +1508,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590098</v>
+        <v>590099</v>
       </c>
       <c r="R9" t="n">
-        <v>6441232</v>
+        <v>6441240</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,7 +1602,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387599</v>
+        <v>122387614</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,35 +1632,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1678,13 +1668,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590106</v>
+        <v>590099</v>
       </c>
       <c r="R10" t="n">
-        <v>6441255</v>
+        <v>6441240</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,7 +1722,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1751,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387614</v>
+        <v>122388072</v>
       </c>
       <c r="B11" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,35 +1752,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1799,13 +1788,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590099</v>
+        <v>590170</v>
       </c>
       <c r="R11" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1832,27 +1821,18 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1871,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122388072</v>
+        <v>122385267</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>90833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,49 +1863,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590170</v>
+        <v>590207</v>
       </c>
       <c r="R12" t="n">
-        <v>6441271</v>
+        <v>6441245</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,6 +1934,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,22 +1954,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122388085</v>
+        <v>122387599</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590192</v>
+        <v>590106</v>
       </c>
       <c r="R13" t="n">
-        <v>6441252</v>
+        <v>6441255</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,9 +2047,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122385267</v>
+        <v>122388005</v>
       </c>
       <c r="B14" t="n">
-        <v>90839</v>
+        <v>105346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,48 +2099,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590207</v>
+        <v>590151</v>
       </c>
       <c r="R14" t="n">
-        <v>6441245</v>
+        <v>6441271</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2173,14 +2168,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,22 +2196,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B15" t="n">
-        <v>105343</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R15" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435277</v>
+        <v>122435302</v>
       </c>
       <c r="B16" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590194</v>
+        <v>590129</v>
       </c>
       <c r="R16" t="n">
-        <v>6441232</v>
+        <v>6441267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435344</v>
+        <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>105346</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,25 +2442,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590106</v>
+        <v>590194</v>
       </c>
       <c r="R17" t="n">
-        <v>6441250</v>
+        <v>6441232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105304</v>
+        <v>105307</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122387641</v>
+        <v>122388079</v>
       </c>
       <c r="B2" t="n">
         <v>98240</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590098</v>
+        <v>590177</v>
       </c>
       <c r="R2" t="n">
-        <v>6441232</v>
+        <v>6441260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +756,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388085</v>
+        <v>122388072</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -844,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590192</v>
+        <v>590170</v>
       </c>
       <c r="R3" t="n">
-        <v>6441252</v>
+        <v>6441271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1028,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387659</v>
+        <v>122387599</v>
       </c>
       <c r="B5" t="n">
         <v>98240</v>
@@ -1076,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590096</v>
+        <v>590106</v>
       </c>
       <c r="R5" t="n">
-        <v>6441257</v>
+        <v>6441255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122388079</v>
+        <v>122385267</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,49 +1151,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590177</v>
+        <v>590207</v>
       </c>
       <c r="R6" t="n">
-        <v>6441260</v>
+        <v>6441245</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,6 +1222,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,12 +1242,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1381,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122385241</v>
+        <v>122387614</v>
       </c>
       <c r="B8" t="n">
-        <v>105307</v>
+        <v>57753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,53 +1387,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590097</v>
+        <v>590099</v>
       </c>
       <c r="R8" t="n">
-        <v>6441248</v>
+        <v>6441240</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,40 +1456,49 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387610</v>
+        <v>122388005</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>105346</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,39 +1507,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1548,13 +1543,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590099</v>
+        <v>590151</v>
       </c>
       <c r="R9" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,6 +1597,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1620,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387614</v>
+        <v>122387610</v>
       </c>
       <c r="B10" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,33 +1628,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388072</v>
+        <v>122385241</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>105307</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,28 +1752,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1784,17 +1788,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590170</v>
+        <v>590097</v>
       </c>
       <c r="R11" t="n">
-        <v>6441271</v>
+        <v>6441248</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,22 +1843,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385267</v>
+        <v>122387659</v>
       </c>
       <c r="B12" t="n">
-        <v>90833</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,48 +1867,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590207</v>
+        <v>590096</v>
       </c>
       <c r="R12" t="n">
-        <v>6441245</v>
+        <v>6441257</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,14 +1936,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,19 +1964,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387599</v>
+        <v>122387641</v>
       </c>
       <c r="B13" t="n">
         <v>98240</v>
@@ -2010,14 +2020,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590106</v>
+        <v>590098</v>
       </c>
       <c r="R13" t="n">
-        <v>6441255</v>
+        <v>6441232</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122388005</v>
+        <v>122388085</v>
       </c>
       <c r="B14" t="n">
-        <v>105346</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,25 +2109,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2135,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590151</v>
+        <v>590192</v>
       </c>
       <c r="R14" t="n">
-        <v>6441271</v>
+        <v>6441252</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,19 +2178,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2319,7 +2319,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435302</v>
+        <v>122435277</v>
       </c>
       <c r="B16" t="n">
         <v>105346</v>
@@ -2363,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590129</v>
+        <v>590194</v>
       </c>
       <c r="R16" t="n">
-        <v>6441267</v>
+        <v>6441232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435277</v>
+        <v>122435302</v>
       </c>
       <c r="B17" t="n">
         <v>105346</v>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590194</v>
+        <v>590129</v>
       </c>
       <c r="R17" t="n">
-        <v>6441232</v>
+        <v>6441267</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122388079</v>
+        <v>122385267</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>90834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590177</v>
+        <v>590207</v>
       </c>
       <c r="R2" t="n">
-        <v>6441260</v>
+        <v>6441245</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388072</v>
+        <v>122387599</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590170</v>
+        <v>590106</v>
       </c>
       <c r="R3" t="n">
-        <v>6441271</v>
+        <v>6441255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,9 +871,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387985</v>
+        <v>122385241</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>105308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,28 +923,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -941,17 +959,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590101</v>
+        <v>590097</v>
       </c>
       <c r="R4" t="n">
-        <v>6441312</v>
+        <v>6441248</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +996,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387599</v>
+        <v>122387641</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,14 +1070,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590106</v>
+        <v>590098</v>
       </c>
       <c r="R5" t="n">
-        <v>6441255</v>
+        <v>6441232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385267</v>
+        <v>122388079</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,48 +1159,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590207</v>
+        <v>590177</v>
       </c>
       <c r="R6" t="n">
-        <v>6441245</v>
+        <v>6441260</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,11 +1231,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,7 +1261,7 @@
         <v>122388002</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387614</v>
+        <v>122387610</v>
       </c>
       <c r="B8" t="n">
-        <v>57753</v>
+        <v>57537</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,33 +1391,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1495,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388005</v>
+        <v>122387614</v>
       </c>
       <c r="B9" t="n">
-        <v>105346</v>
+        <v>57754</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,31 +1519,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1543,13 +1551,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590151</v>
+        <v>590099</v>
       </c>
       <c r="R9" t="n">
-        <v>6441271</v>
+        <v>6441240</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,7 +1605,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1616,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387610</v>
+        <v>122388005</v>
       </c>
       <c r="B10" t="n">
-        <v>57536</v>
+        <v>105347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,39 +1635,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,13 +1671,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590099</v>
+        <v>590151</v>
       </c>
       <c r="R10" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,6 +1725,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1740,10 +1744,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122385241</v>
+        <v>122387985</v>
       </c>
       <c r="B11" t="n">
-        <v>105307</v>
+        <v>98241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,32 +1756,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1788,17 +1788,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590097</v>
+        <v>590101</v>
       </c>
       <c r="R11" t="n">
-        <v>6441248</v>
+        <v>6441312</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1825,9 +1825,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,22 +1853,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387659</v>
+        <v>122388072</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1903,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590096</v>
+        <v>590170</v>
       </c>
       <c r="R12" t="n">
-        <v>6441257</v>
+        <v>6441271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,19 +1946,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387641</v>
+        <v>122387659</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2020,14 +2020,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590098</v>
+        <v>590096</v>
       </c>
       <c r="R13" t="n">
-        <v>6441232</v>
+        <v>6441257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2100,7 +2100,7 @@
         <v>122388085</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435344</v>
+        <v>122435302</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>105347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590106</v>
+        <v>590129</v>
       </c>
       <c r="R15" t="n">
-        <v>6441250</v>
+        <v>6441267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435277</v>
+        <v>122435344</v>
       </c>
       <c r="B16" t="n">
-        <v>105346</v>
+        <v>98241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590194</v>
+        <v>590106</v>
       </c>
       <c r="R16" t="n">
-        <v>6441232</v>
+        <v>6441250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435302</v>
+        <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590129</v>
+        <v>590194</v>
       </c>
       <c r="R17" t="n">
-        <v>6441267</v>
+        <v>6441232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105307</v>
+        <v>105308</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122385267</v>
+        <v>122387641</v>
       </c>
       <c r="B2" t="n">
-        <v>90834</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590207</v>
+        <v>590098</v>
       </c>
       <c r="R2" t="n">
-        <v>6441245</v>
+        <v>6441232</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,14 +756,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122387599</v>
+        <v>122385267</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,49 +808,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590106</v>
+        <v>590207</v>
       </c>
       <c r="R3" t="n">
-        <v>6441255</v>
+        <v>6441245</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,19 +876,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,22 +899,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122385241</v>
+        <v>122387599</v>
       </c>
       <c r="B4" t="n">
-        <v>105308</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,32 +923,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -959,17 +955,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590097</v>
+        <v>590106</v>
       </c>
       <c r="R4" t="n">
-        <v>6441248</v>
+        <v>6441255</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,9 +992,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1020,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387641</v>
+        <v>122388079</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,14 +1076,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590098</v>
+        <v>590177</v>
       </c>
       <c r="R5" t="n">
-        <v>6441232</v>
+        <v>6441260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1113,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122388079</v>
+        <v>122387614</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,35 +1155,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590177</v>
+        <v>590099</v>
       </c>
       <c r="R6" t="n">
-        <v>6441260</v>
+        <v>6441240</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,18 +1224,27 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122388002</v>
+        <v>122387610</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,35 +1275,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1306,13 +1315,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590103</v>
+        <v>590099</v>
       </c>
       <c r="R7" t="n">
-        <v>6441302</v>
+        <v>6441240</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,7 +1369,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1379,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387610</v>
+        <v>122385241</v>
       </c>
       <c r="B8" t="n">
-        <v>57537</v>
+        <v>105311</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,53 +1399,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>340</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590099</v>
+        <v>590097</v>
       </c>
       <c r="R8" t="n">
-        <v>6441240</v>
+        <v>6441248</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1464,49 +1472,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387614</v>
+        <v>122387659</v>
       </c>
       <c r="B9" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,35 +1514,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1551,13 +1550,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590099</v>
+        <v>590096</v>
       </c>
       <c r="R9" t="n">
-        <v>6441240</v>
+        <v>6441257</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122388005</v>
+        <v>122388072</v>
       </c>
       <c r="B10" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,25 +1635,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590151</v>
+        <v>590170</v>
       </c>
       <c r="R10" t="n">
         <v>6441271</v>
@@ -1704,19 +1704,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122387985</v>
+        <v>122388085</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590101</v>
+        <v>590192</v>
       </c>
       <c r="R11" t="n">
-        <v>6441312</v>
+        <v>6441252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,19 +1815,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122388072</v>
+        <v>122388002</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1913,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590170</v>
+        <v>590103</v>
       </c>
       <c r="R12" t="n">
-        <v>6441271</v>
+        <v>6441302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,9 +1926,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387659</v>
+        <v>122387985</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590096</v>
+        <v>590101</v>
       </c>
       <c r="R13" t="n">
-        <v>6441257</v>
+        <v>6441312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2097,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122388085</v>
+        <v>122388005</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>105350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2109,25 +2099,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2145,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590192</v>
+        <v>590151</v>
       </c>
       <c r="R14" t="n">
-        <v>6441252</v>
+        <v>6441271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,9 +2168,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122435302</v>
+        <v>122435344</v>
       </c>
       <c r="B15" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,25 +2220,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590129</v>
+        <v>590106</v>
       </c>
       <c r="R15" t="n">
-        <v>6441267</v>
+        <v>6441250</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435344</v>
+        <v>122435277</v>
       </c>
       <c r="B16" t="n">
-        <v>98241</v>
+        <v>105350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590106</v>
+        <v>590194</v>
       </c>
       <c r="R16" t="n">
-        <v>6441250</v>
+        <v>6441232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435277</v>
+        <v>122435302</v>
       </c>
       <c r="B17" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590194</v>
+        <v>590129</v>
       </c>
       <c r="R17" t="n">
-        <v>6441232</v>
+        <v>6441267</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105308</v>
+        <v>105311</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122387641</v>
+        <v>122388002</v>
       </c>
       <c r="B2" t="n">
         <v>98244</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590098</v>
+        <v>590103</v>
       </c>
       <c r="R2" t="n">
-        <v>6441232</v>
+        <v>6441302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122385267</v>
+        <v>122388085</v>
       </c>
       <c r="B3" t="n">
-        <v>90837</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,48 +808,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590207</v>
+        <v>590192</v>
       </c>
       <c r="R3" t="n">
-        <v>6441245</v>
+        <v>6441252</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,11 +880,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +895,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122387599</v>
+        <v>122388079</v>
       </c>
       <c r="B4" t="n">
         <v>98244</v>
@@ -959,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590106</v>
+        <v>590177</v>
       </c>
       <c r="R4" t="n">
-        <v>6441255</v>
+        <v>6441260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +988,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122388079</v>
+        <v>122387985</v>
       </c>
       <c r="B5" t="n">
         <v>98244</v>
@@ -1080,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590177</v>
+        <v>590101</v>
       </c>
       <c r="R5" t="n">
-        <v>6441260</v>
+        <v>6441312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,9 +1099,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387614</v>
+        <v>122385241</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>105311</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,49 +1151,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>340</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590099</v>
+        <v>590097</v>
       </c>
       <c r="R6" t="n">
-        <v>6441240</v>
+        <v>6441248</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,49 +1224,40 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387610</v>
+        <v>122387614</v>
       </c>
       <c r="B7" t="n">
-        <v>57537</v>
+        <v>57754</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,37 +1266,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1387,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122385241</v>
+        <v>122387599</v>
       </c>
       <c r="B8" t="n">
-        <v>105311</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,32 +1386,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1435,17 +1418,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590097</v>
+        <v>590106</v>
       </c>
       <c r="R8" t="n">
-        <v>6441248</v>
+        <v>6441255</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,9 +1455,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,22 +1483,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122387659</v>
+        <v>122388005</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>105350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,25 +1507,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1550,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590096</v>
+        <v>590151</v>
       </c>
       <c r="R9" t="n">
-        <v>6441257</v>
+        <v>6441271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,7 +1616,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122388072</v>
+        <v>122387641</v>
       </c>
       <c r="B10" t="n">
         <v>98244</v>
@@ -1667,14 +1660,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590170</v>
+        <v>590098</v>
       </c>
       <c r="R10" t="n">
-        <v>6441271</v>
+        <v>6441232</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,9 +1697,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,7 +1737,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388085</v>
+        <v>122388072</v>
       </c>
       <c r="B11" t="n">
         <v>98244</v>
@@ -1782,10 +1785,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590192</v>
+        <v>590170</v>
       </c>
       <c r="R11" t="n">
-        <v>6441252</v>
+        <v>6441271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1845,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122388002</v>
+        <v>122385267</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,49 +1860,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590103</v>
+        <v>590207</v>
       </c>
       <c r="R12" t="n">
-        <v>6441302</v>
+        <v>6441245</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1926,19 +1928,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,22 +1951,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387985</v>
+        <v>122387610</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>57537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,35 +1975,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2014,13 +2015,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590101</v>
+        <v>590099</v>
       </c>
       <c r="R13" t="n">
-        <v>6441312</v>
+        <v>6441240</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2068,7 +2069,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2087,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122388005</v>
+        <v>122387659</v>
       </c>
       <c r="B14" t="n">
-        <v>105350</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,25 +2099,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590151</v>
+        <v>590096</v>
       </c>
       <c r="R14" t="n">
-        <v>6441271</v>
+        <v>6441257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387985</v>
+        <v>122385241</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>105311</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,28 +1030,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1062,17 +1066,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590101</v>
+        <v>590097</v>
       </c>
       <c r="R5" t="n">
-        <v>6441312</v>
+        <v>6441248</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,19 +1103,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385241</v>
+        <v>122387985</v>
       </c>
       <c r="B6" t="n">
-        <v>105311</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,32 +1145,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1187,17 +1177,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590097</v>
+        <v>590101</v>
       </c>
       <c r="R6" t="n">
-        <v>6441248</v>
+        <v>6441312</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,9 +1214,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1242,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122385267</v>
+        <v>122387610</v>
       </c>
       <c r="B12" t="n">
-        <v>90837</v>
+        <v>57537</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,44 +1864,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590207</v>
+        <v>590099</v>
       </c>
       <c r="R12" t="n">
-        <v>6441245</v>
+        <v>6441240</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,14 +1933,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,29 +1954,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122387610</v>
+        <v>122385267</v>
       </c>
       <c r="B13" t="n">
-        <v>57537</v>
+        <v>90837</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,49 +1988,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590099</v>
+        <v>590207</v>
       </c>
       <c r="R13" t="n">
-        <v>6441240</v>
+        <v>6441245</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2048,19 +2052,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,18 +2068,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387610</v>
+        <v>122385267</v>
       </c>
       <c r="B12" t="n">
-        <v>57537</v>
+        <v>90837</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,49 +1864,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590099</v>
+        <v>590207</v>
       </c>
       <c r="R12" t="n">
-        <v>6441240</v>
+        <v>6441245</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,19 +1928,14 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,28 +1944,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385267</v>
+        <v>122387610</v>
       </c>
       <c r="B13" t="n">
-        <v>90837</v>
+        <v>57537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,44 +1979,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590207</v>
+        <v>590099</v>
       </c>
       <c r="R13" t="n">
-        <v>6441245</v>
+        <v>6441240</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,14 +2048,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,19 +2069,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122385241</v>
+        <v>122387985</v>
       </c>
       <c r="B5" t="n">
-        <v>105311</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,32 +1030,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>340</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1066,17 +1062,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590097</v>
+        <v>590101</v>
       </c>
       <c r="R5" t="n">
-        <v>6441248</v>
+        <v>6441312</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,9 +1099,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1127,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122387985</v>
+        <v>122385241</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>105311</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,28 +1151,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1177,17 +1187,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590101</v>
+        <v>590097</v>
       </c>
       <c r="R6" t="n">
-        <v>6441312</v>
+        <v>6441248</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,19 +1224,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1242,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>122435344</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435277</v>
+        <v>122435302</v>
       </c>
       <c r="B16" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,14 +2363,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A1779, Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590194</v>
+        <v>590129</v>
       </c>
       <c r="R16" t="n">
-        <v>6441232</v>
+        <v>6441267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122435302</v>
+        <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,14 +2474,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A1779, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590129</v>
+        <v>590194</v>
       </c>
       <c r="R17" t="n">
-        <v>6441267</v>
+        <v>6441232</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105311</v>
+        <v>105414</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>122449135</v>
       </c>
       <c r="B18" t="n">
-        <v>105414</v>
+        <v>105422</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 2806-2025 artfynd.xlsx
+++ b/artfynd/A 2806-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122388002</v>
+        <v>122385241</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,24 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -719,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590103</v>
+        <v>590097</v>
       </c>
       <c r="R2" t="n">
-        <v>6441302</v>
+        <v>6441248</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,19 +755,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122388085</v>
+        <v>122449135</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,45 +796,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>340</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Öndal, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590192</v>
+        <v>590097</v>
       </c>
       <c r="R3" t="n">
-        <v>6441252</v>
+        <v>6441254</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,14 +857,19 @@
           <t>Ukna</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Hf-Väs-1974</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,80 +878,82 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Åke Rühling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122388079</v>
+        <v>122385267</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>Avverkningsanmälan Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590177</v>
+        <v>590207</v>
       </c>
       <c r="R4" t="n">
-        <v>6441260</v>
+        <v>6441245</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,59 +1003,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122387985</v>
+        <v>122387614</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590101</v>
+        <v>590099</v>
       </c>
       <c r="R5" t="n">
-        <v>6441312</v>
+        <v>6441240</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1112,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,65 +1130,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122385241</v>
+        <v>122387610</v>
       </c>
       <c r="B6" t="n">
-        <v>105311</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>340</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590097</v>
+        <v>590099</v>
       </c>
       <c r="R6" t="n">
-        <v>6441248</v>
+        <v>6441240</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,77 +1210,81 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122387614</v>
+        <v>122387599</v>
       </c>
       <c r="B7" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,13 +1292,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590099</v>
+        <v>590106</v>
       </c>
       <c r="R7" t="n">
-        <v>6441240</v>
+        <v>6441255</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,6 +1346,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1374,15 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122387599</v>
+        <v>122387641</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,14 +1404,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 2806, Svartgöl, Sm</t>
+          <t>A 2806, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590106</v>
+        <v>590098</v>
       </c>
       <c r="R8" t="n">
-        <v>6441255</v>
+        <v>6441232</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,37 +1481,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122388005</v>
+        <v>122387659</v>
       </c>
       <c r="B9" t="n">
-        <v>105350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590151</v>
+        <v>590096</v>
       </c>
       <c r="R9" t="n">
-        <v>6441271</v>
+        <v>6441257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,15 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122387641</v>
+        <v>122387985</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,14 +1636,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 2806, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590098</v>
+        <v>590101</v>
       </c>
       <c r="R10" t="n">
-        <v>6441232</v>
+        <v>6441312</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,15 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122388072</v>
+        <v>122388002</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590170</v>
+        <v>590103</v>
       </c>
       <c r="R11" t="n">
-        <v>6441271</v>
+        <v>6441302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,9 +1789,19 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,51 +1829,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122387610</v>
+        <v>122388072</v>
       </c>
       <c r="B12" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1900,13 +1872,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590099</v>
+        <v>590170</v>
       </c>
       <c r="R12" t="n">
-        <v>6441240</v>
+        <v>6441271</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1933,27 +1905,18 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1972,60 +1935,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122385267</v>
+        <v>122388079</v>
       </c>
       <c r="B13" t="n">
-        <v>90837</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Avverkningsanmälan Svartgöl, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590207</v>
+        <v>590177</v>
       </c>
       <c r="R13" t="n">
-        <v>6441245</v>
+        <v>6441260</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,11 +2014,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,27 +2029,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122387659</v>
+        <v>122388085</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590096</v>
+        <v>590192</v>
       </c>
       <c r="R14" t="n">
-        <v>6441257</v>
+        <v>6441252</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,19 +2117,9 @@
           <t>2025-01-30</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,12 +2150,7 @@
         <v>122435344</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,15 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122435302</v>
+        <v>122388005</v>
       </c>
       <c r="B16" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590129</v>
+        <v>590151</v>
       </c>
       <c r="R16" t="n">
-        <v>6441267</v>
+        <v>6441271</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,12 +2326,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,7 +2362,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2433,12 +2372,7 @@
         <v>122435277</v>
       </c>
       <c r="B17" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2541,62 +2475,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122449135</v>
+        <v>122435302</v>
       </c>
       <c r="B18" t="n">
-        <v>105422</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>340</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öndal, Sm</t>
+          <t>A 2806, Svartgöl, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590097</v>
+        <v>590129</v>
       </c>
       <c r="R18" t="n">
-        <v>6441254</v>
+        <v>6441267</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2618,19 +2546,14 @@
           <t>Ukna</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Hf-Väs-1974</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,30 +2562,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Åke Rühling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
